--- a/THA.xlsx
+++ b/THA.xlsx
@@ -474,7 +474,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N2" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -521,7 +521,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -533,7 +533,7 @@
         <v/>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N3" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -568,7 +568,7 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -580,7 +580,7 @@
         <v/>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N4" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -615,7 +615,7 @@
         <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -627,7 +627,7 @@
         <v/>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N5" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -662,7 +662,7 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -674,7 +674,7 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N6" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -709,7 +709,7 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -721,7 +721,7 @@
         <v/>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N7" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -756,7 +756,7 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -768,7 +768,7 @@
         <v/>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N8" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -815,7 +815,7 @@
         <v/>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N9" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -850,7 +850,7 @@
         <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -862,7 +862,7 @@
         <v/>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N10" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -897,7 +897,7 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N11" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -944,7 +944,7 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -956,7 +956,7 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N12" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -991,7 +991,7 @@
         <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -1003,7 +1003,7 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N13" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -1038,7 +1038,7 @@
         <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1050,7 +1050,7 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N14" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -1085,7 +1085,7 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N15" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -1132,7 +1132,7 @@
         <v/>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N16" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -1273,7 +1273,7 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1285,7 +1285,7 @@
         <v/>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N19" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -1320,7 +1320,7 @@
         <v/>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1332,7 +1332,7 @@
         <v/>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N20" t="str">
         <v/>

--- a/THA.xlsx
+++ b/THA.xlsx
@@ -1367,7 +1367,7 @@
         <v/>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Gönderildi</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1379,7 +1379,7 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>Evet</v>
       </c>
       <c r="N21" t="str">
         <v/>
